--- a/backend/data/financials_by_company/0159.HK.xlsx
+++ b/backend/data/financials_by_company/0159.HK.xlsx
@@ -3826,7 +3826,7 @@
         <v>-27168000</v>
       </c>
       <c r="BN2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO2" t="n">
         <v>-35.453</v>
@@ -4048,7 +4048,7 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW2" t="n">
         <v>0.0022799969</v>
